--- a/agent_runs/manjidiwang/episodes/ep04/storyboard_index.xlsx
+++ b/agent_runs/manjidiwang/episodes/ep04/storyboard_index.xlsx
@@ -84,7 +84,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>考场答题 （，总时长：12秒，镜头数：3个）</t>
+          <t>考场答题</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -132,7 +132,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>考官发难 （，总时长：10秒，镜头数：5个）</t>
+          <t>考官发难</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -180,7 +180,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>压分离场 （，总时长：11秒，镜头数：4个）</t>
+          <t>压分离场</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -228,7 +228,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>走廊嘲讽 （，总时长：11秒，镜头数：5个）</t>
+          <t>走廊嘲讽</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -276,7 +276,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>嚣张反讽与离去 （，总时长：11秒，镜头数：5个）</t>
+          <t>嚣张反讽与离去</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>书房震怒 （，总时长：13秒，镜头数：5个）</t>
+          <t>书房震怒</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -372,7 +372,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>甜枣补偿 （，总时长：10秒，镜头数：4个）</t>
+          <t>甜枣补偿</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -420,7 +420,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>灯下黑 （，总时长：10秒，镜头数：4个）</t>
+          <t>灯下黑</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>证据属实与门铃 （，总时长：10秒，镜头数：4个）</t>
+          <t>证据属实与门铃</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>妹妹跪诉 （，总时长：12秒，镜头数：4个）</t>
+          <t>妹妹跪诉</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>三条条件（上） （，总时长：10秒，镜头数：3个）</t>
+          <t>三条条件（上）</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>第三条与成交 （，总时长：12秒，镜头数：3个）</t>
+          <t>第三条与成交</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>窗外心声 （，总时长：11秒，镜头数：4个）</t>
+          <t>窗外心声</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
